--- a/motivation/WayStar_Матрица_и_показатели.xlsx
+++ b/motivation/WayStar_Матрица_и_показатели.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,7 +49,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -75,9 +75,23 @@
       <sz val="10"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006B7A8D"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <name val="Calibri"/>
-      <color rgb="006B7A8D"/>
-      <sz val="8.5"/>
+      <b val="1"/>
+      <color rgb="002F6690"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -90,20 +104,11 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00C4772F"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="002E7D46"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="006B7A8D"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -150,7 +155,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -172,14 +177,53 @@
         <color rgb="00C9D3DE"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C9D3DE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9D3DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D3DE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9D3DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D3DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -192,8 +236,11 @@
     <xf numFmtId="3" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -210,30 +257,30 @@
     <xf numFmtId="3" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -262,7 +309,7 @@
     <xf numFmtId="9" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -628,890 +675,1002 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ТОО «WayStar Group» · Матрица структуры оплаты труда 75/25 и показателей</t>
+          <t>ТОО «WayStar Group» · Матрица оплаты 75/25 и показателей</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Приложение 1 к приказу о введении оплаты «75% постоянная + 25% переменная» (с 01.01.2026). «Факт KPI, %» подтягивается с листа «Показатели (детально)». Премия = Лимит × мин(100%; факт) — по приказу не выше лимита 25%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+          <t>Приложение 1 к приказу (75/25, с 01.01.2026). Три уровня суммы: «на руки», «брутто (оклад)», «полная стоимость (ФОТ)». База деления 75/25 выбирается ячейкой-переключателем ниже; премия = Лимит × мин(100%; факт), не выше лимита (приказ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>База деления 75/25:</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Брутто (оклад)</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>← выберите: на руки / брутто (оклад) / полная стоимость (ФОТ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Подразделение</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Должность</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>ФИО</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Табельный №/ID</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Целевой ежемесячный доход (100%), ₸</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Таб. №</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>На руки (100%), ₸</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Брутто/оклад (100%), ₸</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Полная стоимость (100%), ₸</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Целевой доход по базе (100%), ₸</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Оклад (75%), ₸</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Лимит премии (25%), ₸</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Дата начала действия</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>Дата начала</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>Факт KPI, %</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>Начисленная премия, ₸</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Итого (оклад+премия), ₸</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Руководство</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Президент</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Серикбаев Адиль</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D6" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E6" s="10" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F6" s="10" t="n">
         <v>6000139</v>
       </c>
-      <c r="F5" s="6">
-        <f>E5*0.75</f>
-        <v/>
-      </c>
-      <c r="G5" s="6">
-        <f>E5*0.25</f>
-        <v/>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="G6" s="10" t="n">
+        <v>6613107</v>
+      </c>
+      <c r="H6" s="11">
+        <f>IF($C$3="На руки",E6,IF($C$3="Брутто (оклад)",F6,G6))</f>
+        <v/>
+      </c>
+      <c r="I6" s="10">
+        <f>H6*0.75</f>
+        <v/>
+      </c>
+      <c r="J6" s="10">
+        <f>H6*0.25</f>
+        <v/>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Отвечает за весь результат</t>
-        </is>
-      </c>
-      <c r="J5" s="8">
+      <c r="L6" s="13">
         <f>'Показатели (детально)'!E11</f>
         <v/>
       </c>
-      <c r="K5" s="9">
-        <f>G5*MIN(1,J5)</f>
-        <v/>
-      </c>
-      <c r="L5" s="9">
-        <f>F5+K5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="M6" s="14">
+        <f>J6*MIN(1,L6)</f>
+        <v/>
+      </c>
+      <c r="N6" s="14">
+        <f>I6+M6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Руководство</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Генеральный директор</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Данияр Алим</t>
         </is>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D7" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E7" s="17" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F7" s="17" t="n">
         <v>1246243</v>
       </c>
-      <c r="F6" s="12">
-        <f>E6*0.75</f>
-        <v/>
-      </c>
-      <c r="G6" s="12">
-        <f>E6*0.25</f>
-        <v/>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="G7" s="17" t="n">
+        <v>1422801</v>
+      </c>
+      <c r="H7" s="18">
+        <f>IF($C$3="На руки",E7,IF($C$3="Брутто (оклад)",F7,G7))</f>
+        <v/>
+      </c>
+      <c r="I7" s="17">
+        <f>H7*0.75</f>
+        <v/>
+      </c>
+      <c r="J7" s="17">
+        <f>H7*0.25</f>
+        <v/>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
         <is>
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>Операционный результат</t>
-        </is>
-      </c>
-      <c r="J6" s="8">
+      <c r="L7" s="13">
         <f>'Показатели (детально)'!E20</f>
         <v/>
       </c>
-      <c r="K6" s="14">
-        <f>G6*MIN(1,J6)</f>
-        <v/>
-      </c>
-      <c r="L6" s="14">
-        <f>F6+K6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="M7" s="20">
+        <f>J7*MIN(1,L7)</f>
+        <v/>
+      </c>
+      <c r="N7" s="20">
+        <f>I7+M7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Финансы</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Финансовый директор</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Аубакиров Алимбек</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E8" s="10" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="F8" s="10" t="n">
         <v>4347889</v>
       </c>
-      <c r="F7" s="6">
-        <f>E7*0.75</f>
-        <v/>
-      </c>
-      <c r="G7" s="6">
-        <f>E7*0.25</f>
-        <v/>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="G8" s="10" t="n">
+        <v>4861722</v>
+      </c>
+      <c r="H8" s="11">
+        <f>IF($C$3="На руки",E8,IF($C$3="Брутто (оклад)",F8,G8))</f>
+        <v/>
+      </c>
+      <c r="I8" s="10">
+        <f>H8*0.75</f>
+        <v/>
+      </c>
+      <c r="J8" s="10">
+        <f>H8*0.25</f>
+        <v/>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
         <is>
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Прибыль и денежная устойчивость</t>
-        </is>
-      </c>
-      <c r="J7" s="8">
+      <c r="L8" s="13">
         <f>'Показатели (детально)'!E29</f>
         <v/>
       </c>
-      <c r="K7" s="9">
-        <f>G7*MIN(1,J7)</f>
-        <v/>
-      </c>
-      <c r="L7" s="9">
-        <f>F7+K7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="M8" s="14">
+        <f>J8*MIN(1,L8)</f>
+        <v/>
+      </c>
+      <c r="N8" s="14">
+        <f>I8+M8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Операции</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Операционный директор</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Унбетпаев Ернар</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D9" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E9" s="17" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="F9" s="17" t="n">
         <v>1873611</v>
       </c>
-      <c r="F8" s="12">
-        <f>E8*0.75</f>
-        <v/>
-      </c>
-      <c r="G8" s="12">
-        <f>E8*0.25</f>
-        <v/>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="G9" s="17" t="n">
+        <v>2124280</v>
+      </c>
+      <c r="H9" s="18">
+        <f>IF($C$3="На руки",E9,IF($C$3="Брутто (оклад)",F9,G9))</f>
+        <v/>
+      </c>
+      <c r="I9" s="17">
+        <f>H9*0.75</f>
+        <v/>
+      </c>
+      <c r="J9" s="17">
+        <f>H9*0.25</f>
+        <v/>
+      </c>
+      <c r="K9" s="19" t="inlineStr">
         <is>
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>Валовая прибыль по операциям ≥ K× стоимости</t>
-        </is>
-      </c>
-      <c r="J8" s="8">
+      <c r="L9" s="13">
         <f>'Показатели (детально)'!E38</f>
         <v/>
       </c>
-      <c r="K8" s="14">
-        <f>G8*MIN(1,J8)</f>
-        <v/>
-      </c>
-      <c r="L8" s="14">
-        <f>F8+K8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="M9" s="20">
+        <f>J9*MIN(1,L9)</f>
+        <v/>
+      </c>
+      <c r="N9" s="20">
+        <f>I9+M9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Начальник отдела логистики</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Доолоткулов Данияр</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D10" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E10" s="10" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F10" s="10" t="n">
         <v>1246243</v>
       </c>
-      <c r="F9" s="6">
-        <f>E9*0.75</f>
-        <v/>
-      </c>
-      <c r="G9" s="6">
-        <f>E9*0.25</f>
-        <v/>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="G10" s="10" t="n">
+        <v>1422801</v>
+      </c>
+      <c r="H10" s="11">
+        <f>IF($C$3="На руки",E10,IF($C$3="Брутто (оклад)",F10,G10))</f>
+        <v/>
+      </c>
+      <c r="I10" s="10">
+        <f>H10*0.75</f>
+        <v/>
+      </c>
+      <c r="J10" s="10">
+        <f>H10*0.25</f>
+        <v/>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
         <is>
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Валовая прибыль отдела ≥ K× стоимости</t>
-        </is>
-      </c>
-      <c r="J9" s="8">
+      <c r="L10" s="13">
         <f>'Показатели (детально)'!E47</f>
         <v/>
       </c>
-      <c r="K9" s="9">
-        <f>G9*MIN(1,J9)</f>
-        <v/>
-      </c>
-      <c r="L9" s="9">
-        <f>F9+K9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="M10" s="14">
+        <f>J10*MIN(1,L10)</f>
+        <v/>
+      </c>
+      <c r="N10" s="14">
+        <f>I10+M10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Менеджер по логистике (старший)</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Сибагатов Хамардин</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D11" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E11" s="17" t="n">
+        <v>800000</v>
+      </c>
+      <c r="F11" s="17" t="n">
         <v>993718</v>
       </c>
-      <c r="F10" s="12">
-        <f>E10*0.75</f>
-        <v/>
-      </c>
-      <c r="G10" s="12">
-        <f>E10*0.25</f>
-        <v/>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="G11" s="17" t="n">
+        <v>1140528</v>
+      </c>
+      <c r="H11" s="18">
+        <f>IF($C$3="На руки",E11,IF($C$3="Брутто (оклад)",F11,G11))</f>
+        <v/>
+      </c>
+      <c r="I11" s="17">
+        <f>H11*0.75</f>
+        <v/>
+      </c>
+      <c r="J11" s="17">
+        <f>H11*0.25</f>
+        <v/>
+      </c>
+      <c r="K11" s="19" t="inlineStr">
         <is>
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>Маржа ≥ K× стоимости; наставничество</t>
-        </is>
-      </c>
-      <c r="J10" s="8">
+      <c r="L11" s="13">
         <f>'Показатели (детально)'!E56</f>
         <v/>
       </c>
-      <c r="K10" s="14">
-        <f>G10*MIN(1,J10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="14">
-        <f>F10+K10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="M11" s="20">
+        <f>J11*MIN(1,L11)</f>
+        <v/>
+      </c>
+      <c r="N11" s="20">
+        <f>I11+M11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Менеджер по логистике</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Жунусова Камила</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E12" s="10" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F12" s="10" t="n">
         <v>230896</v>
       </c>
-      <c r="F11" s="6">
-        <f>E11*0.75</f>
-        <v/>
-      </c>
-      <c r="G11" s="6">
-        <f>E11*0.25</f>
-        <v/>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="G12" s="10" t="n">
+        <v>261836</v>
+      </c>
+      <c r="H12" s="11">
+        <f>IF($C$3="На руки",E12,IF($C$3="Брутто (оклад)",F12,G12))</f>
+        <v/>
+      </c>
+      <c r="I12" s="10">
+        <f>H12*0.75</f>
+        <v/>
+      </c>
+      <c r="J12" s="10">
+        <f>H12*0.25</f>
+        <v/>
+      </c>
+      <c r="K12" s="12" t="inlineStr">
         <is>
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Маржа ≥ K× стоимости</t>
-        </is>
-      </c>
-      <c r="J11" s="8">
+      <c r="L12" s="13">
         <f>'Показатели (детально)'!E65</f>
         <v/>
       </c>
-      <c r="K11" s="9">
-        <f>G11*MIN(1,J11)</f>
-        <v/>
-      </c>
-      <c r="L11" s="9">
-        <f>F11+K11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="M12" s="14">
+        <f>J12*MIN(1,L12)</f>
+        <v/>
+      </c>
+      <c r="N12" s="14">
+        <f>I12+M12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Менеджер по логистике</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>Сейтқадыр Дарын</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D13" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E13" s="17" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F13" s="17" t="n">
         <v>236143</v>
       </c>
-      <c r="F12" s="12">
-        <f>E12*0.75</f>
-        <v/>
-      </c>
-      <c r="G12" s="12">
-        <f>E12*0.25</f>
-        <v/>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="G13" s="17" t="n">
+        <v>274587</v>
+      </c>
+      <c r="H13" s="18">
+        <f>IF($C$3="На руки",E13,IF($C$3="Брутто (оклад)",F13,G13))</f>
+        <v/>
+      </c>
+      <c r="I13" s="17">
+        <f>H13*0.75</f>
+        <v/>
+      </c>
+      <c r="J13" s="17">
+        <f>H13*0.25</f>
+        <v/>
+      </c>
+      <c r="K13" s="19" t="inlineStr">
         <is>
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>Маржа ≥ K× стоимости</t>
-        </is>
-      </c>
-      <c r="J12" s="8">
+      <c r="L13" s="13">
         <f>'Показатели (детально)'!E74</f>
         <v/>
       </c>
-      <c r="K12" s="14">
-        <f>G12*MIN(1,J12)</f>
-        <v/>
-      </c>
-      <c r="L12" s="14">
-        <f>F12+K12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="M13" s="20">
+        <f>J13*MIN(1,L13)</f>
+        <v/>
+      </c>
+      <c r="N13" s="20">
+        <f>I13+M13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Менеджер по логистике (младший)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Белова Полина</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D14" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E14" s="10" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F14" s="10" t="n">
         <v>173011</v>
       </c>
-      <c r="F13" s="6">
-        <f>E13*0.75</f>
-        <v/>
-      </c>
-      <c r="G13" s="6">
-        <f>E13*0.25</f>
-        <v/>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="G14" s="10" t="n">
+        <v>201177</v>
+      </c>
+      <c r="H14" s="11">
+        <f>IF($C$3="На руки",E14,IF($C$3="Брутто (оклад)",F14,G14))</f>
+        <v/>
+      </c>
+      <c r="I14" s="10">
+        <f>H14*0.75</f>
+        <v/>
+      </c>
+      <c r="J14" s="10">
+        <f>H14*0.25</f>
+        <v/>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
         <is>
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Маржа ≥ K× стоимости; пороги ниже</t>
-        </is>
-      </c>
-      <c r="J13" s="8">
+      <c r="L14" s="13">
         <f>'Показатели (детально)'!E83</f>
         <v/>
       </c>
-      <c r="K13" s="9">
-        <f>G13*MIN(1,J13)</f>
-        <v/>
-      </c>
-      <c r="L13" s="9">
-        <f>F13+K13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="M14" s="14">
+        <f>J14*MIN(1,L14)</f>
+        <v/>
+      </c>
+      <c r="N14" s="14">
+        <f>I14+M14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Расчёты</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Менеджер по закрытию</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Таджимурадова Асем</t>
         </is>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D15" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E15" s="17" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F15" s="17" t="n">
         <v>378788</v>
       </c>
-      <c r="F14" s="12">
-        <f>E14*0.75</f>
-        <v/>
-      </c>
-      <c r="G14" s="12">
-        <f>E14*0.25</f>
-        <v/>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="G15" s="17" t="n">
+        <v>440456</v>
+      </c>
+      <c r="H15" s="18">
+        <f>IF($C$3="На руки",E15,IF($C$3="Брутто (оклад)",F15,G15))</f>
+        <v/>
+      </c>
+      <c r="I15" s="17">
+        <f>H15*0.75</f>
+        <v/>
+      </c>
+      <c r="J15" s="17">
+        <f>H15*0.25</f>
+        <v/>
+      </c>
+      <c r="K15" s="19" t="inlineStr">
         <is>
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>Прибыль по закрытым перевозкам + собранная оплата</t>
-        </is>
-      </c>
-      <c r="J14" s="8">
+      <c r="L15" s="13">
         <f>'Показатели (детально)'!E91</f>
         <v/>
       </c>
-      <c r="K14" s="14">
-        <f>G14*MIN(1,J14)</f>
-        <v/>
-      </c>
-      <c r="L14" s="14">
-        <f>F14+K14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="M15" s="20">
+        <f>J15*MIN(1,L15)</f>
+        <v/>
+      </c>
+      <c r="N15" s="20">
+        <f>I15+M15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Персонал</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Руководитель отдела персонала</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Аманбекова Айгуль</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6" t="n">
+      <c r="D16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F16" s="10" t="n">
         <v>1246243</v>
       </c>
-      <c r="F15" s="6">
-        <f>E15*0.75</f>
-        <v/>
-      </c>
-      <c r="G15" s="6">
-        <f>E15*0.25</f>
-        <v/>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="G16" s="10" t="n">
+        <v>1379182</v>
+      </c>
+      <c r="H16" s="11">
+        <f>IF($C$3="На руки",E16,IF($C$3="Брутто (оклад)",F16,G16))</f>
+        <v/>
+      </c>
+      <c r="I16" s="10">
+        <f>H16*0.75</f>
+        <v/>
+      </c>
+      <c r="J16" s="10">
+        <f>H16*0.25</f>
+        <v/>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
         <is>
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Поддержка · доля от прибыли компании</t>
-        </is>
-      </c>
-      <c r="J15" s="8">
+      <c r="L16" s="13">
         <f>'Показатели (детально)'!E100</f>
         <v/>
       </c>
-      <c r="K15" s="9">
-        <f>G15*MIN(1,J15)</f>
-        <v/>
-      </c>
-      <c r="L15" s="9">
-        <f>F15+K15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="M16" s="14">
+        <f>J16*MIN(1,L16)</f>
+        <v/>
+      </c>
+      <c r="N16" s="14">
+        <f>I16+M16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Персонал</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Менеджер по персоналу</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Байльденова Шолпан</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D17" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E17" s="17" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F17" s="17" t="n">
         <v>614931</v>
       </c>
-      <c r="F16" s="12">
-        <f>E16*0.75</f>
-        <v/>
-      </c>
-      <c r="G16" s="12">
-        <f>E16*0.25</f>
-        <v/>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="G17" s="17" t="n">
+        <v>715042</v>
+      </c>
+      <c r="H17" s="18">
+        <f>IF($C$3="На руки",E17,IF($C$3="Брутто (оклад)",F17,G17))</f>
+        <v/>
+      </c>
+      <c r="I17" s="17">
+        <f>H17*0.75</f>
+        <v/>
+      </c>
+      <c r="J17" s="17">
+        <f>H17*0.25</f>
+        <v/>
+      </c>
+      <c r="K17" s="19" t="inlineStr">
         <is>
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>Поддержка · доля от прибыли компании</t>
-        </is>
-      </c>
-      <c r="J16" s="8">
+      <c r="L17" s="13">
         <f>'Показатели (детально)'!E109</f>
         <v/>
       </c>
-      <c r="K16" s="14">
-        <f>G16*MIN(1,J16)</f>
-        <v/>
-      </c>
-      <c r="L16" s="14">
-        <f>F16+K16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="M17" s="20">
+        <f>J17*MIN(1,L17)</f>
+        <v/>
+      </c>
+      <c r="N17" s="20">
+        <f>I17+M17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Юридический</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Юрист</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Ташметов Сакен</t>
         </is>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D18" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E18" s="10" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F18" s="10" t="n">
         <v>1246243</v>
       </c>
-      <c r="F17" s="6">
-        <f>E17*0.75</f>
-        <v/>
-      </c>
-      <c r="G17" s="6">
-        <f>E17*0.25</f>
-        <v/>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="G18" s="10" t="n">
+        <v>1422801</v>
+      </c>
+      <c r="H18" s="11">
+        <f>IF($C$3="На руки",E18,IF($C$3="Брутто (оклад)",F18,G18))</f>
+        <v/>
+      </c>
+      <c r="I18" s="10">
+        <f>H18*0.75</f>
+        <v/>
+      </c>
+      <c r="J18" s="10">
+        <f>H18*0.25</f>
+        <v/>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
         <is>
           <t>01.01.2026</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>Поддержка · доля от прибыли компании</t>
-        </is>
-      </c>
-      <c r="J17" s="8">
+      <c r="L18" s="13">
         <f>'Показатели (детально)'!E118</f>
         <v/>
       </c>
-      <c r="K17" s="9">
-        <f>G17*MIN(1,J17)</f>
-        <v/>
-      </c>
-      <c r="L17" s="9">
-        <f>F17+K17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="M18" s="14">
+        <f>J18*MIN(1,L18)</f>
+        <v/>
+      </c>
+      <c r="N18" s="14">
+        <f>I18+M18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="n"/>
+      <c r="B19" s="21" t="n"/>
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="16">
-        <f>SUM(E5:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="16">
-        <f>SUM(F5:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="16">
-        <f>SUM(G5:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
-      <c r="K18" s="16">
-        <f>SUM(K5:K17)</f>
-        <v/>
-      </c>
-      <c r="L18" s="16">
-        <f>SUM(L5:L17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" s="17" t="inlineStr">
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="22">
+        <f>SUM(E6:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="22">
+        <f>SUM(F6:F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="22">
+        <f>SUM(G6:G18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="22">
+        <f>SUM(H6:H18)</f>
+        <v/>
+      </c>
+      <c r="I19" s="22">
+        <f>SUM(I6:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="22">
+        <f>SUM(J6:J18)</f>
+        <v/>
+      </c>
+      <c r="K19" s="21" t="n"/>
+      <c r="L19" s="21" t="n"/>
+      <c r="M19" s="22">
+        <f>SUM(M6:M18)</f>
+        <v/>
+      </c>
+      <c r="N19" s="22">
+        <f>SUM(N6:N18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>В год (×12), ₸:</t>
         </is>
       </c>
-      <c r="E20" s="18">
-        <f>E18*12</f>
-        <v/>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>Лимит премий/год (под результатом):</t>
-        </is>
-      </c>
-      <c r="K20" s="20">
-        <f>K18*12</f>
-        <v/>
-      </c>
-      <c r="L20" s="21">
-        <f>L18*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>• Целевой ежемесячный доход (100%) = действующий оклад начисленный; из него 75% — постоянная часть, 25% — лимит премии.</t>
-        </is>
+      <c r="H21" s="23">
+        <f>H19*12</f>
+        <v/>
+      </c>
+      <c r="J21" s="24">
+        <f>J19*12</f>
+        <v/>
+      </c>
+      <c r="M21" s="24">
+        <f>M19*12</f>
+        <v/>
+      </c>
+      <c r="N21" s="25">
+        <f>N19*12</f>
+        <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
-        <is>
-          <t>• Факт KPI, % — итоговое выполнение показателей с листа «Показатели (детально)» (вводится там, жёлтые ячейки).</t>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>• Три уровня: «на руки» (нетто), «брутто/оклад» (начисленный), «полная стоимость» (ФОТ со всеми налогами работодателя).</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>• Начисленная премия = Лимит × мин(100%; Факт KPI). По приказу (п.4.3) премия не превышает лимит переменной части (25%).</t>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>• Ячейка C3 — переключатель базы: «Целевой доход по базе» и деление 75/25 пересчитываются автоматически.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
-        <is>
-          <t>• Переменная может быть снижена/не выплачена при нарушениях дисциплины, сроков/качества (приказ п.4.4) — корректируется вручную.</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>• Для трудового договора оклад указывается в брутто. При базе «на руки»/«полная стоимость» оклад (75%) — пересчитать в брутто перед договором.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>• Табельный № — временный (порядковый); заменить на реальные ID при внедрении.</t>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>• Начисленная премия = Лимит × мин(100%; Факт KPI). По приказу (п.4.3) премия не превышает лимит (25%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>• Факт KPI, % — с листа «Показатели (детально)» (вводится там). Таб. № — временный, заменить на реальные ID.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="G20"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A22:L22"/>
+  <mergeCells count="9">
+    <mergeCell ref="A27:N27"/>
+    <mergeCell ref="A26:N26"/>
+    <mergeCell ref="A24:N24"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="A25:N25"/>
+    <mergeCell ref="A23:N23"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A3:B3"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="C3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"На руки,Брутто (оклад),Полная стоимость (ФОТ)"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1548,1922 +1707,1922 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="n"/>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="A4" s="26" t="n"/>
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Серикбаев Адиль — Президент · Руководство  [ПЕРЕДОВАЯ ЛИНИЯ]</t>
         </is>
       </c>
-      <c r="C4" s="23" t="n"/>
-      <c r="D4" s="23" t="n"/>
-      <c r="E4" s="23" t="n"/>
-      <c r="F4" s="23" t="n"/>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="26" t="n"/>
+      <c r="F4" s="26" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="A5" s="27" t="n"/>
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Вес</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Выполнение, %</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Вклад</t>
         </is>
       </c>
-      <c r="F5" s="24" t="n"/>
+      <c r="F5" s="27" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="n"/>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="A6" s="28" t="n"/>
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Чистая прибыль компании к плану</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="30" t="n">
         <v>0.5</v>
       </c>
-      <c r="D6" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="27">
+      <c r="D6" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="30">
         <f>C6*D6</f>
         <v/>
       </c>
-      <c r="F6" s="25" t="n"/>
+      <c r="F6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="n"/>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="A7" s="28" t="n"/>
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Выручка к плану</t>
         </is>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D7" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="30">
+      <c r="D7" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="33">
         <f>C7*D7</f>
         <v/>
       </c>
-      <c r="F7" s="25" t="n"/>
+      <c r="F7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="n"/>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="A8" s="28" t="n"/>
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>Развитие: направления/клиенты/география</t>
         </is>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="D8" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="30">
+      <c r="D8" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="33">
         <f>C8*D8</f>
         <v/>
       </c>
-      <c r="F8" s="25" t="n"/>
+      <c r="F8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="n"/>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="A9" s="28" t="n"/>
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Денежный поток / финансирование</t>
         </is>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="33" t="n">
         <v>0.1</v>
       </c>
-      <c r="D9" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="30">
+      <c r="D9" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="33">
         <f>C9*D9</f>
         <v/>
       </c>
-      <c r="F9" s="25" t="n"/>
+      <c r="F9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="n"/>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="n"/>
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>Удержание ключевой команды</t>
         </is>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="33" t="n">
         <v>0.05</v>
       </c>
-      <c r="D10" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="30">
+      <c r="D10" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="33">
         <f>C10*D10</f>
         <v/>
       </c>
-      <c r="F10" s="25" t="n"/>
+      <c r="F10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="n"/>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="A11" s="34" t="n"/>
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>Итоговое выполнение показателей</t>
         </is>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="36">
         <f>SUM(C6:C10)</f>
         <v/>
       </c>
-      <c r="D11" s="31" t="n"/>
-      <c r="E11" s="34">
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="37">
         <f>SUM(E6:E10)</f>
         <v/>
       </c>
-      <c r="F11" s="31" t="n"/>
+      <c r="F11" s="34" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="n"/>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="A13" s="26" t="n"/>
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>Данияр Алим — Генеральный директор · Руководство  [ПЕРЕДОВАЯ ЛИНИЯ]</t>
         </is>
       </c>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="23" t="n"/>
-      <c r="F13" s="23" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="26" t="n"/>
+      <c r="F13" s="26" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="n"/>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="27" t="n"/>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Вес</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Выполнение, %</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Вклад</t>
         </is>
       </c>
-      <c r="F14" s="24" t="n"/>
+      <c r="F14" s="27" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="n"/>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="A15" s="28" t="n"/>
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>Чистая прибыль компании к плану</t>
         </is>
       </c>
-      <c r="C15" s="27" t="n">
+      <c r="C15" s="30" t="n">
         <v>0.4</v>
       </c>
-      <c r="D15" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="27">
+      <c r="D15" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="30">
         <f>C15*D15</f>
         <v/>
       </c>
-      <c r="F15" s="25" t="n"/>
+      <c r="F15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="n"/>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="A16" s="28" t="n"/>
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>Валовая прибыль / рентабельность</t>
         </is>
       </c>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="30" t="n">
         <v>0.2</v>
       </c>
-      <c r="D16" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="27">
+      <c r="D16" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="30">
         <f>C16*D16</f>
         <v/>
       </c>
-      <c r="F16" s="25" t="n"/>
+      <c r="F16" s="28" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="n"/>
-      <c r="B17" s="29" t="inlineStr">
+      <c r="A17" s="28" t="n"/>
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Выручка к плану</t>
         </is>
       </c>
-      <c r="C17" s="30" t="n">
+      <c r="C17" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="D17" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="30">
+      <c r="D17" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="33">
         <f>C17*D17</f>
         <v/>
       </c>
-      <c r="F17" s="25" t="n"/>
+      <c r="F17" s="28" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="n"/>
-      <c r="B18" s="29" t="inlineStr">
+      <c r="A18" s="28" t="n"/>
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>Выполнение годового плана</t>
         </is>
       </c>
-      <c r="C18" s="30" t="n">
+      <c r="C18" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D18" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="30">
+      <c r="D18" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="33">
         <f>C18*D18</f>
         <v/>
       </c>
-      <c r="F18" s="25" t="n"/>
+      <c r="F18" s="28" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="n"/>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="A19" s="28" t="n"/>
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>Удержание клиентов</t>
         </is>
       </c>
-      <c r="C19" s="30" t="n">
+      <c r="C19" s="33" t="n">
         <v>0.05</v>
       </c>
-      <c r="D19" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="30">
+      <c r="D19" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="33">
         <f>C19*D19</f>
         <v/>
       </c>
-      <c r="F19" s="25" t="n"/>
+      <c r="F19" s="28" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="31" t="n"/>
-      <c r="B20" s="32" t="inlineStr">
+      <c r="A20" s="34" t="n"/>
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Итоговое выполнение показателей</t>
         </is>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="36">
         <f>SUM(C15:C19)</f>
         <v/>
       </c>
-      <c r="D20" s="31" t="n"/>
-      <c r="E20" s="34">
+      <c r="D20" s="34" t="n"/>
+      <c r="E20" s="37">
         <f>SUM(E15:E19)</f>
         <v/>
       </c>
-      <c r="F20" s="31" t="n"/>
+      <c r="F20" s="34" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="n"/>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="A22" s="26" t="n"/>
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Аубакиров Алимбек — Финансовый директор · Финансы  [ПЕРЕДОВАЯ ЛИНИЯ]</t>
         </is>
       </c>
-      <c r="C22" s="23" t="n"/>
-      <c r="D22" s="23" t="n"/>
-      <c r="E22" s="23" t="n"/>
-      <c r="F22" s="23" t="n"/>
+      <c r="C22" s="26" t="n"/>
+      <c r="D22" s="26" t="n"/>
+      <c r="E22" s="26" t="n"/>
+      <c r="F22" s="26" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="A23" s="27" t="n"/>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Вес</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Выполнение, %</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>Вклад</t>
         </is>
       </c>
-      <c r="F23" s="24" t="n"/>
+      <c r="F23" s="27" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="n"/>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="A24" s="28" t="n"/>
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>Чистая прибыль компании к плану</t>
         </is>
       </c>
-      <c r="C24" s="27" t="n">
+      <c r="C24" s="30" t="n">
         <v>0.35</v>
       </c>
-      <c r="D24" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="27">
+      <c r="D24" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="30">
         <f>C24*D24</f>
         <v/>
       </c>
-      <c r="F24" s="25" t="n"/>
+      <c r="F24" s="28" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="n"/>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="A25" s="28" t="n"/>
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>Запас денежных средств</t>
         </is>
       </c>
-      <c r="C25" s="30" t="n">
+      <c r="C25" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="D25" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="30">
+      <c r="D25" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="33">
         <f>C25*D25</f>
         <v/>
       </c>
-      <c r="F25" s="25" t="n"/>
+      <c r="F25" s="28" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="n"/>
-      <c r="B26" s="29" t="inlineStr">
+      <c r="A26" s="28" t="n"/>
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>Оборот дебиторской задолженности</t>
         </is>
       </c>
-      <c r="C26" s="30" t="n">
+      <c r="C26" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D26" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="30">
+      <c r="D26" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="33">
         <f>C26*D26</f>
         <v/>
       </c>
-      <c r="F26" s="25" t="n"/>
+      <c r="F26" s="28" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="25" t="n"/>
-      <c r="B27" s="29" t="inlineStr">
+      <c r="A27" s="28" t="n"/>
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>Точность бюджета</t>
         </is>
       </c>
-      <c r="C27" s="30" t="n">
+      <c r="C27" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D27" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="30">
+      <c r="D27" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="33">
         <f>C27*D27</f>
         <v/>
       </c>
-      <c r="F27" s="25" t="n"/>
+      <c r="F27" s="28" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="n"/>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="A28" s="28" t="n"/>
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>Привлечение финансирования</t>
         </is>
       </c>
-      <c r="C28" s="30" t="n">
+      <c r="C28" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D28" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="30">
+      <c r="D28" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="33">
         <f>C28*D28</f>
         <v/>
       </c>
-      <c r="F28" s="25" t="n"/>
+      <c r="F28" s="28" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="31" t="n"/>
-      <c r="B29" s="32" t="inlineStr">
+      <c r="A29" s="34" t="n"/>
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>Итоговое выполнение показателей</t>
         </is>
       </c>
-      <c r="C29" s="33">
+      <c r="C29" s="36">
         <f>SUM(C24:C28)</f>
         <v/>
       </c>
-      <c r="D29" s="31" t="n"/>
-      <c r="E29" s="34">
+      <c r="D29" s="34" t="n"/>
+      <c r="E29" s="37">
         <f>SUM(E24:E28)</f>
         <v/>
       </c>
-      <c r="F29" s="31" t="n"/>
+      <c r="F29" s="34" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="n"/>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="A31" s="26" t="n"/>
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>Унбетпаев Ернар — Операционный директор · Операции  [ПЕРЕДОВАЯ ЛИНИЯ]</t>
         </is>
       </c>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="23" t="n"/>
-      <c r="E31" s="23" t="n"/>
-      <c r="F31" s="23" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+      <c r="E31" s="26" t="n"/>
+      <c r="F31" s="26" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="24" t="n"/>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="A32" s="27" t="n"/>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Вес</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>Выполнение, %</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>Вклад</t>
         </is>
       </c>
-      <c r="F32" s="24" t="n"/>
+      <c r="F32" s="27" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="25" t="n"/>
-      <c r="B33" s="26" t="inlineStr">
+      <c r="A33" s="28" t="n"/>
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t>Валовая прибыль по операциям к плану</t>
         </is>
       </c>
-      <c r="C33" s="27" t="n">
+      <c r="C33" s="30" t="n">
         <v>0.4</v>
       </c>
-      <c r="D33" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="27">
+      <c r="D33" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="30">
         <f>C33*D33</f>
         <v/>
       </c>
-      <c r="F33" s="25" t="n"/>
+      <c r="F33" s="28" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="n"/>
-      <c r="B34" s="29" t="inlineStr">
+      <c r="A34" s="28" t="n"/>
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>Соблюдение сроков (в срок и полностью)</t>
         </is>
       </c>
-      <c r="C34" s="30" t="n">
+      <c r="C34" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="D34" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="30">
+      <c r="D34" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="33">
         <f>C34*D34</f>
         <v/>
       </c>
-      <c r="F34" s="25" t="n"/>
+      <c r="F34" s="28" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="25" t="n"/>
-      <c r="B35" s="29" t="inlineStr">
+      <c r="A35" s="28" t="n"/>
+      <c r="B35" s="32" t="inlineStr">
         <is>
           <t>Себестоимость операций на тонну/км</t>
         </is>
       </c>
-      <c r="C35" s="30" t="n">
+      <c r="C35" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="D35" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="30">
+      <c r="D35" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="33">
         <f>C35*D35</f>
         <v/>
       </c>
-      <c r="F35" s="25" t="n"/>
+      <c r="F35" s="28" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="25" t="n"/>
-      <c r="B36" s="29" t="inlineStr">
+      <c r="A36" s="28" t="n"/>
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>Безопасность / охрана труда</t>
         </is>
       </c>
-      <c r="C36" s="30" t="n">
+      <c r="C36" s="33" t="n">
         <v>0.1</v>
       </c>
-      <c r="D36" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="30">
+      <c r="D36" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="33">
         <f>C36*D36</f>
         <v/>
       </c>
-      <c r="F36" s="25" t="n"/>
+      <c r="F36" s="28" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="25" t="n"/>
-      <c r="B37" s="29" t="inlineStr">
+      <c r="A37" s="28" t="n"/>
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t>Загрузка / порожний пробег</t>
         </is>
       </c>
-      <c r="C37" s="30" t="n">
+      <c r="C37" s="33" t="n">
         <v>0.1</v>
       </c>
-      <c r="D37" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="30">
+      <c r="D37" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="33">
         <f>C37*D37</f>
         <v/>
       </c>
-      <c r="F37" s="25" t="n"/>
+      <c r="F37" s="28" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="31" t="n"/>
-      <c r="B38" s="32" t="inlineStr">
+      <c r="A38" s="34" t="n"/>
+      <c r="B38" s="35" t="inlineStr">
         <is>
           <t>Итоговое выполнение показателей</t>
         </is>
       </c>
-      <c r="C38" s="33">
+      <c r="C38" s="36">
         <f>SUM(C33:C37)</f>
         <v/>
       </c>
-      <c r="D38" s="31" t="n"/>
-      <c r="E38" s="34">
+      <c r="D38" s="34" t="n"/>
+      <c r="E38" s="37">
         <f>SUM(E33:E37)</f>
         <v/>
       </c>
-      <c r="F38" s="31" t="n"/>
+      <c r="F38" s="34" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="n"/>
-      <c r="B40" s="23" t="inlineStr">
+      <c r="A40" s="26" t="n"/>
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>Доолоткулов Данияр — Начальник отдела логистики · Логистика  [ПЕРЕДОВАЯ ЛИНИЯ]</t>
         </is>
       </c>
-      <c r="C40" s="23" t="n"/>
-      <c r="D40" s="23" t="n"/>
-      <c r="E40" s="23" t="n"/>
-      <c r="F40" s="23" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+      <c r="E40" s="26" t="n"/>
+      <c r="F40" s="26" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="A41" s="27" t="n"/>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Вес</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Выполнение, %</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>Вклад</t>
         </is>
       </c>
-      <c r="F41" s="24" t="n"/>
+      <c r="F41" s="27" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="25" t="n"/>
-      <c r="B42" s="26" t="inlineStr">
+      <c r="A42" s="28" t="n"/>
+      <c r="B42" s="29" t="inlineStr">
         <is>
           <t>Валовая прибыль отдела перевозок к плану</t>
         </is>
       </c>
-      <c r="C42" s="27" t="n">
+      <c r="C42" s="30" t="n">
         <v>0.4</v>
       </c>
-      <c r="D42" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="27">
+      <c r="D42" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="30">
         <f>C42*D42</f>
         <v/>
       </c>
-      <c r="F42" s="25" t="n"/>
+      <c r="F42" s="28" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="25" t="n"/>
-      <c r="B43" s="29" t="inlineStr">
+      <c r="A43" s="28" t="n"/>
+      <c r="B43" s="32" t="inlineStr">
         <is>
           <t>Соблюдение сроков доставки</t>
         </is>
       </c>
-      <c r="C43" s="30" t="n">
+      <c r="C43" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="D43" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="30">
+      <c r="D43" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="33">
         <f>C43*D43</f>
         <v/>
       </c>
-      <c r="F43" s="25" t="n"/>
+      <c r="F43" s="28" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="25" t="n"/>
-      <c r="B44" s="29" t="inlineStr">
+      <c r="A44" s="28" t="n"/>
+      <c r="B44" s="32" t="inlineStr">
         <is>
           <t>Себестоимость перевозки на рейс/тонну</t>
         </is>
       </c>
-      <c r="C44" s="30" t="n">
+      <c r="C44" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="D44" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="30">
+      <c r="D44" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="33">
         <f>C44*D44</f>
         <v/>
       </c>
-      <c r="F44" s="25" t="n"/>
+      <c r="F44" s="28" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="25" t="n"/>
-      <c r="B45" s="29" t="inlineStr">
+      <c r="A45" s="28" t="n"/>
+      <c r="B45" s="32" t="inlineStr">
         <is>
           <t>Загрузка / порожний пробег</t>
         </is>
       </c>
-      <c r="C45" s="30" t="n">
+      <c r="C45" s="33" t="n">
         <v>0.1</v>
       </c>
-      <c r="D45" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="30">
+      <c r="D45" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="33">
         <f>C45*D45</f>
         <v/>
       </c>
-      <c r="F45" s="25" t="n"/>
+      <c r="F45" s="28" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="25" t="n"/>
-      <c r="B46" s="29" t="inlineStr">
+      <c r="A46" s="28" t="n"/>
+      <c r="B46" s="32" t="inlineStr">
         <is>
           <t>Сохранность груза / претензии</t>
         </is>
       </c>
-      <c r="C46" s="30" t="n">
+      <c r="C46" s="33" t="n">
         <v>0.1</v>
       </c>
-      <c r="D46" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="30">
+      <c r="D46" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="33">
         <f>C46*D46</f>
         <v/>
       </c>
-      <c r="F46" s="25" t="n"/>
+      <c r="F46" s="28" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="31" t="n"/>
-      <c r="B47" s="32" t="inlineStr">
+      <c r="A47" s="34" t="n"/>
+      <c r="B47" s="35" t="inlineStr">
         <is>
           <t>Итоговое выполнение показателей</t>
         </is>
       </c>
-      <c r="C47" s="33">
+      <c r="C47" s="36">
         <f>SUM(C42:C46)</f>
         <v/>
       </c>
-      <c r="D47" s="31" t="n"/>
-      <c r="E47" s="34">
+      <c r="D47" s="34" t="n"/>
+      <c r="E47" s="37">
         <f>SUM(E42:E46)</f>
         <v/>
       </c>
-      <c r="F47" s="31" t="n"/>
+      <c r="F47" s="34" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="23" t="n"/>
-      <c r="B49" s="23" t="inlineStr">
+      <c r="A49" s="26" t="n"/>
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>Сибагатов Хамардин — Менеджер по логистике (старший) · Логистика  [ПЕРЕДОВАЯ ЛИНИЯ]</t>
         </is>
       </c>
-      <c r="C49" s="23" t="n"/>
-      <c r="D49" s="23" t="n"/>
-      <c r="E49" s="23" t="n"/>
-      <c r="F49" s="23" t="n"/>
+      <c r="C49" s="26" t="n"/>
+      <c r="D49" s="26" t="n"/>
+      <c r="E49" s="26" t="n"/>
+      <c r="F49" s="26" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="24" t="n"/>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="A50" s="27" t="n"/>
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Вес</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Выполнение, %</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>Вклад</t>
         </is>
       </c>
-      <c r="F50" s="24" t="n"/>
+      <c r="F50" s="27" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="25" t="n"/>
-      <c r="B51" s="26" t="inlineStr">
+      <c r="A51" s="28" t="n"/>
+      <c r="B51" s="29" t="inlineStr">
         <is>
           <t>Валовая маржа по своим перевозкам (≥K×стоимости)</t>
         </is>
       </c>
-      <c r="C51" s="27" t="n">
+      <c r="C51" s="30" t="n">
         <v>0.45</v>
       </c>
-      <c r="D51" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="27">
+      <c r="D51" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="30">
         <f>C51*D51</f>
         <v/>
       </c>
-      <c r="F51" s="25" t="n"/>
+      <c r="F51" s="28" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="25" t="n"/>
-      <c r="B52" s="29" t="inlineStr">
+      <c r="A52" s="28" t="n"/>
+      <c r="B52" s="32" t="inlineStr">
         <is>
           <t>Объём перевозок к норме</t>
         </is>
       </c>
-      <c r="C52" s="30" t="n">
+      <c r="C52" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D52" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="30">
+      <c r="D52" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="33">
         <f>C52*D52</f>
         <v/>
       </c>
-      <c r="F52" s="25" t="n"/>
+      <c r="F52" s="28" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="25" t="n"/>
-      <c r="B53" s="29" t="inlineStr">
+      <c r="A53" s="28" t="n"/>
+      <c r="B53" s="32" t="inlineStr">
         <is>
           <t>Соблюдение сроков доставки</t>
         </is>
       </c>
-      <c r="C53" s="30" t="n">
+      <c r="C53" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D53" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="30">
+      <c r="D53" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="33">
         <f>C53*D53</f>
         <v/>
       </c>
-      <c r="F53" s="25" t="n"/>
+      <c r="F53" s="28" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="25" t="n"/>
-      <c r="B54" s="29" t="inlineStr">
+      <c r="A54" s="28" t="n"/>
+      <c r="B54" s="32" t="inlineStr">
         <is>
           <t>Загрузка / порожний пробег</t>
         </is>
       </c>
-      <c r="C54" s="30" t="n">
+      <c r="C54" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D54" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="30">
+      <c r="D54" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="33">
         <f>C54*D54</f>
         <v/>
       </c>
-      <c r="F54" s="25" t="n"/>
+      <c r="F54" s="28" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="25" t="n"/>
-      <c r="B55" s="29" t="inlineStr">
+      <c r="A55" s="28" t="n"/>
+      <c r="B55" s="32" t="inlineStr">
         <is>
           <t>Точность документов / сохранность</t>
         </is>
       </c>
-      <c r="C55" s="30" t="n">
+      <c r="C55" s="33" t="n">
         <v>0.1</v>
       </c>
-      <c r="D55" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="30">
+      <c r="D55" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="33">
         <f>C55*D55</f>
         <v/>
       </c>
-      <c r="F55" s="25" t="n"/>
+      <c r="F55" s="28" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="31" t="n"/>
-      <c r="B56" s="32" t="inlineStr">
+      <c r="A56" s="34" t="n"/>
+      <c r="B56" s="35" t="inlineStr">
         <is>
           <t>Итоговое выполнение показателей</t>
         </is>
       </c>
-      <c r="C56" s="33">
+      <c r="C56" s="36">
         <f>SUM(C51:C55)</f>
         <v/>
       </c>
-      <c r="D56" s="31" t="n"/>
-      <c r="E56" s="34">
+      <c r="D56" s="34" t="n"/>
+      <c r="E56" s="37">
         <f>SUM(E51:E55)</f>
         <v/>
       </c>
-      <c r="F56" s="31" t="n"/>
+      <c r="F56" s="34" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="23" t="n"/>
-      <c r="B58" s="23" t="inlineStr">
+      <c r="A58" s="26" t="n"/>
+      <c r="B58" s="26" t="inlineStr">
         <is>
           <t>Жунусова Камила — Менеджер по логистике · Логистика  [ПЕРЕДОВАЯ ЛИНИЯ]</t>
         </is>
       </c>
-      <c r="C58" s="23" t="n"/>
-      <c r="D58" s="23" t="n"/>
-      <c r="E58" s="23" t="n"/>
-      <c r="F58" s="23" t="n"/>
+      <c r="C58" s="26" t="n"/>
+      <c r="D58" s="26" t="n"/>
+      <c r="E58" s="26" t="n"/>
+      <c r="F58" s="26" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="24" t="n"/>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="A59" s="27" t="n"/>
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Вес</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>Выполнение, %</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>Вклад</t>
         </is>
       </c>
-      <c r="F59" s="24" t="n"/>
+      <c r="F59" s="27" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="25" t="n"/>
-      <c r="B60" s="26" t="inlineStr">
+      <c r="A60" s="28" t="n"/>
+      <c r="B60" s="29" t="inlineStr">
         <is>
           <t>Валовая маржа по своим перевозкам (≥K×стоимости)</t>
         </is>
       </c>
-      <c r="C60" s="27" t="n">
+      <c r="C60" s="30" t="n">
         <v>0.45</v>
       </c>
-      <c r="D60" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="27">
+      <c r="D60" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="30">
         <f>C60*D60</f>
         <v/>
       </c>
-      <c r="F60" s="25" t="n"/>
+      <c r="F60" s="28" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="25" t="n"/>
-      <c r="B61" s="29" t="inlineStr">
+      <c r="A61" s="28" t="n"/>
+      <c r="B61" s="32" t="inlineStr">
         <is>
           <t>Объём перевозок к норме</t>
         </is>
       </c>
-      <c r="C61" s="30" t="n">
+      <c r="C61" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D61" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="30">
+      <c r="D61" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="33">
         <f>C61*D61</f>
         <v/>
       </c>
-      <c r="F61" s="25" t="n"/>
+      <c r="F61" s="28" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="25" t="n"/>
-      <c r="B62" s="29" t="inlineStr">
+      <c r="A62" s="28" t="n"/>
+      <c r="B62" s="32" t="inlineStr">
         <is>
           <t>Соблюдение сроков доставки</t>
         </is>
       </c>
-      <c r="C62" s="30" t="n">
+      <c r="C62" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D62" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="30">
+      <c r="D62" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="33">
         <f>C62*D62</f>
         <v/>
       </c>
-      <c r="F62" s="25" t="n"/>
+      <c r="F62" s="28" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="25" t="n"/>
-      <c r="B63" s="29" t="inlineStr">
+      <c r="A63" s="28" t="n"/>
+      <c r="B63" s="32" t="inlineStr">
         <is>
           <t>Загрузка / порожний пробег</t>
         </is>
       </c>
-      <c r="C63" s="30" t="n">
+      <c r="C63" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D63" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="30">
+      <c r="D63" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="33">
         <f>C63*D63</f>
         <v/>
       </c>
-      <c r="F63" s="25" t="n"/>
+      <c r="F63" s="28" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="25" t="n"/>
-      <c r="B64" s="29" t="inlineStr">
+      <c r="A64" s="28" t="n"/>
+      <c r="B64" s="32" t="inlineStr">
         <is>
           <t>Точность документов / сохранность</t>
         </is>
       </c>
-      <c r="C64" s="30" t="n">
+      <c r="C64" s="33" t="n">
         <v>0.1</v>
       </c>
-      <c r="D64" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="30">
+      <c r="D64" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="33">
         <f>C64*D64</f>
         <v/>
       </c>
-      <c r="F64" s="25" t="n"/>
+      <c r="F64" s="28" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="31" t="n"/>
-      <c r="B65" s="32" t="inlineStr">
+      <c r="A65" s="34" t="n"/>
+      <c r="B65" s="35" t="inlineStr">
         <is>
           <t>Итоговое выполнение показателей</t>
         </is>
       </c>
-      <c r="C65" s="33">
+      <c r="C65" s="36">
         <f>SUM(C60:C64)</f>
         <v/>
       </c>
-      <c r="D65" s="31" t="n"/>
-      <c r="E65" s="34">
+      <c r="D65" s="34" t="n"/>
+      <c r="E65" s="37">
         <f>SUM(E60:E64)</f>
         <v/>
       </c>
-      <c r="F65" s="31" t="n"/>
+      <c r="F65" s="34" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="23" t="n"/>
-      <c r="B67" s="23" t="inlineStr">
+      <c r="A67" s="26" t="n"/>
+      <c r="B67" s="26" t="inlineStr">
         <is>
           <t>Сейтқадыр Дарын — Менеджер по логистике · Логистика  [ПЕРЕДОВАЯ ЛИНИЯ]</t>
         </is>
       </c>
-      <c r="C67" s="23" t="n"/>
-      <c r="D67" s="23" t="n"/>
-      <c r="E67" s="23" t="n"/>
-      <c r="F67" s="23" t="n"/>
+      <c r="C67" s="26" t="n"/>
+      <c r="D67" s="26" t="n"/>
+      <c r="E67" s="26" t="n"/>
+      <c r="F67" s="26" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="24" t="n"/>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="A68" s="27" t="n"/>
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>Вес</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>Выполнение, %</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>Вклад</t>
         </is>
       </c>
-      <c r="F68" s="24" t="n"/>
+      <c r="F68" s="27" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="25" t="n"/>
-      <c r="B69" s="26" t="inlineStr">
+      <c r="A69" s="28" t="n"/>
+      <c r="B69" s="29" t="inlineStr">
         <is>
           <t>Валовая маржа по своим перевозкам (≥K×стоимости)</t>
         </is>
       </c>
-      <c r="C69" s="27" t="n">
+      <c r="C69" s="30" t="n">
         <v>0.45</v>
       </c>
-      <c r="D69" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="27">
+      <c r="D69" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="30">
         <f>C69*D69</f>
         <v/>
       </c>
-      <c r="F69" s="25" t="n"/>
+      <c r="F69" s="28" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="25" t="n"/>
-      <c r="B70" s="29" t="inlineStr">
+      <c r="A70" s="28" t="n"/>
+      <c r="B70" s="32" t="inlineStr">
         <is>
           <t>Объём перевозок к норме</t>
         </is>
       </c>
-      <c r="C70" s="30" t="n">
+      <c r="C70" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D70" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="30">
+      <c r="D70" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="33">
         <f>C70*D70</f>
         <v/>
       </c>
-      <c r="F70" s="25" t="n"/>
+      <c r="F70" s="28" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="25" t="n"/>
-      <c r="B71" s="29" t="inlineStr">
+      <c r="A71" s="28" t="n"/>
+      <c r="B71" s="32" t="inlineStr">
         <is>
           <t>Соблюдение сроков доставки</t>
         </is>
       </c>
-      <c r="C71" s="30" t="n">
+      <c r="C71" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D71" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="30">
+      <c r="D71" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="33">
         <f>C71*D71</f>
         <v/>
       </c>
-      <c r="F71" s="25" t="n"/>
+      <c r="F71" s="28" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="25" t="n"/>
-      <c r="B72" s="29" t="inlineStr">
+      <c r="A72" s="28" t="n"/>
+      <c r="B72" s="32" t="inlineStr">
         <is>
           <t>Загрузка / порожний пробег</t>
         </is>
       </c>
-      <c r="C72" s="30" t="n">
+      <c r="C72" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D72" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="30">
+      <c r="D72" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="33">
         <f>C72*D72</f>
         <v/>
       </c>
-      <c r="F72" s="25" t="n"/>
+      <c r="F72" s="28" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="25" t="n"/>
-      <c r="B73" s="29" t="inlineStr">
+      <c r="A73" s="28" t="n"/>
+      <c r="B73" s="32" t="inlineStr">
         <is>
           <t>Точность документов / сохранность</t>
         </is>
       </c>
-      <c r="C73" s="30" t="n">
+      <c r="C73" s="33" t="n">
         <v>0.1</v>
       </c>
-      <c r="D73" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="30">
+      <c r="D73" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="33">
         <f>C73*D73</f>
         <v/>
       </c>
-      <c r="F73" s="25" t="n"/>
+      <c r="F73" s="28" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="31" t="n"/>
-      <c r="B74" s="32" t="inlineStr">
+      <c r="A74" s="34" t="n"/>
+      <c r="B74" s="35" t="inlineStr">
         <is>
           <t>Итоговое выполнение показателей</t>
         </is>
       </c>
-      <c r="C74" s="33">
+      <c r="C74" s="36">
         <f>SUM(C69:C73)</f>
         <v/>
       </c>
-      <c r="D74" s="31" t="n"/>
-      <c r="E74" s="34">
+      <c r="D74" s="34" t="n"/>
+      <c r="E74" s="37">
         <f>SUM(E69:E73)</f>
         <v/>
       </c>
-      <c r="F74" s="31" t="n"/>
+      <c r="F74" s="34" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="23" t="n"/>
-      <c r="B76" s="23" t="inlineStr">
+      <c r="A76" s="26" t="n"/>
+      <c r="B76" s="26" t="inlineStr">
         <is>
           <t>Белова Полина — Менеджер по логистике (младший) · Логистика  [ПЕРЕДОВАЯ ЛИНИЯ]</t>
         </is>
       </c>
-      <c r="C76" s="23" t="n"/>
-      <c r="D76" s="23" t="n"/>
-      <c r="E76" s="23" t="n"/>
-      <c r="F76" s="23" t="n"/>
+      <c r="C76" s="26" t="n"/>
+      <c r="D76" s="26" t="n"/>
+      <c r="E76" s="26" t="n"/>
+      <c r="F76" s="26" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="24" t="n"/>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="A77" s="27" t="n"/>
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>Вес</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>Выполнение, %</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>Вклад</t>
         </is>
       </c>
-      <c r="F77" s="24" t="n"/>
+      <c r="F77" s="27" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="25" t="n"/>
-      <c r="B78" s="26" t="inlineStr">
+      <c r="A78" s="28" t="n"/>
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>Валовая маржа по своим перевозкам (≥K×стоимости)</t>
         </is>
       </c>
-      <c r="C78" s="27" t="n">
+      <c r="C78" s="30" t="n">
         <v>0.45</v>
       </c>
-      <c r="D78" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="27">
+      <c r="D78" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="30">
         <f>C78*D78</f>
         <v/>
       </c>
-      <c r="F78" s="25" t="n"/>
+      <c r="F78" s="28" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="25" t="n"/>
-      <c r="B79" s="29" t="inlineStr">
+      <c r="A79" s="28" t="n"/>
+      <c r="B79" s="32" t="inlineStr">
         <is>
           <t>Объём перевозок к норме</t>
         </is>
       </c>
-      <c r="C79" s="30" t="n">
+      <c r="C79" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D79" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="30">
+      <c r="D79" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="33">
         <f>C79*D79</f>
         <v/>
       </c>
-      <c r="F79" s="25" t="n"/>
+      <c r="F79" s="28" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="25" t="n"/>
-      <c r="B80" s="29" t="inlineStr">
+      <c r="A80" s="28" t="n"/>
+      <c r="B80" s="32" t="inlineStr">
         <is>
           <t>Соблюдение сроков доставки</t>
         </is>
       </c>
-      <c r="C80" s="30" t="n">
+      <c r="C80" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D80" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="30">
+      <c r="D80" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="33">
         <f>C80*D80</f>
         <v/>
       </c>
-      <c r="F80" s="25" t="n"/>
+      <c r="F80" s="28" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="25" t="n"/>
-      <c r="B81" s="29" t="inlineStr">
+      <c r="A81" s="28" t="n"/>
+      <c r="B81" s="32" t="inlineStr">
         <is>
           <t>Загрузка / порожний пробег</t>
         </is>
       </c>
-      <c r="C81" s="30" t="n">
+      <c r="C81" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D81" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="30">
+      <c r="D81" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="33">
         <f>C81*D81</f>
         <v/>
       </c>
-      <c r="F81" s="25" t="n"/>
+      <c r="F81" s="28" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="25" t="n"/>
-      <c r="B82" s="29" t="inlineStr">
+      <c r="A82" s="28" t="n"/>
+      <c r="B82" s="32" t="inlineStr">
         <is>
           <t>Точность документов / сохранность</t>
         </is>
       </c>
-      <c r="C82" s="30" t="n">
+      <c r="C82" s="33" t="n">
         <v>0.1</v>
       </c>
-      <c r="D82" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="30">
+      <c r="D82" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="33">
         <f>C82*D82</f>
         <v/>
       </c>
-      <c r="F82" s="25" t="n"/>
+      <c r="F82" s="28" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="31" t="n"/>
-      <c r="B83" s="32" t="inlineStr">
+      <c r="A83" s="34" t="n"/>
+      <c r="B83" s="35" t="inlineStr">
         <is>
           <t>Итоговое выполнение показателей</t>
         </is>
       </c>
-      <c r="C83" s="33">
+      <c r="C83" s="36">
         <f>SUM(C78:C82)</f>
         <v/>
       </c>
-      <c r="D83" s="31" t="n"/>
-      <c r="E83" s="34">
+      <c r="D83" s="34" t="n"/>
+      <c r="E83" s="37">
         <f>SUM(E78:E82)</f>
         <v/>
       </c>
-      <c r="F83" s="31" t="n"/>
+      <c r="F83" s="34" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="23" t="n"/>
-      <c r="B85" s="23" t="inlineStr">
+      <c r="A85" s="26" t="n"/>
+      <c r="B85" s="26" t="inlineStr">
         <is>
           <t>Таджимурадова Асем — Менеджер по закрытию · Расчёты  [ПЕРЕДОВАЯ ЛИНИЯ]</t>
         </is>
       </c>
-      <c r="C85" s="23" t="n"/>
-      <c r="D85" s="23" t="n"/>
-      <c r="E85" s="23" t="n"/>
-      <c r="F85" s="23" t="n"/>
+      <c r="C85" s="26" t="n"/>
+      <c r="D85" s="26" t="n"/>
+      <c r="E85" s="26" t="n"/>
+      <c r="F85" s="26" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="24" t="n"/>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="A86" s="27" t="n"/>
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>Вес</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>Выполнение, %</t>
         </is>
       </c>
-      <c r="E86" s="3" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>Вклад</t>
         </is>
       </c>
-      <c r="F86" s="24" t="n"/>
+      <c r="F86" s="27" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="25" t="n"/>
-      <c r="B87" s="26" t="inlineStr">
+      <c r="A87" s="28" t="n"/>
+      <c r="B87" s="29" t="inlineStr">
         <is>
           <t>Валовая прибыль по закрытым перевозкам к плану</t>
         </is>
       </c>
-      <c r="C87" s="27" t="n">
+      <c r="C87" s="30" t="n">
         <v>0.45</v>
       </c>
-      <c r="D87" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="27">
+      <c r="D87" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="30">
         <f>C87*D87</f>
         <v/>
       </c>
-      <c r="F87" s="25" t="n"/>
+      <c r="F87" s="28" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="25" t="n"/>
-      <c r="B88" s="29" t="inlineStr">
+      <c r="A88" s="28" t="n"/>
+      <c r="B88" s="32" t="inlineStr">
         <is>
           <t>Собираемость оплаты в срок</t>
         </is>
       </c>
-      <c r="C88" s="30" t="n">
+      <c r="C88" s="33" t="n">
         <v>0.3</v>
       </c>
-      <c r="D88" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="30">
+      <c r="D88" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="33">
         <f>C88*D88</f>
         <v/>
       </c>
-      <c r="F88" s="25" t="n"/>
+      <c r="F88" s="28" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="25" t="n"/>
-      <c r="B89" s="29" t="inlineStr">
+      <c r="A89" s="28" t="n"/>
+      <c r="B89" s="32" t="inlineStr">
         <is>
           <t>Срок закрытия документов</t>
         </is>
       </c>
-      <c r="C89" s="30" t="n">
+      <c r="C89" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D89" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="30">
+      <c r="D89" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="33">
         <f>C89*D89</f>
         <v/>
       </c>
-      <c r="F89" s="25" t="n"/>
+      <c r="F89" s="28" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="25" t="n"/>
-      <c r="B90" s="29" t="inlineStr">
+      <c r="A90" s="28" t="n"/>
+      <c r="B90" s="32" t="inlineStr">
         <is>
           <t>Точность / отсутствие расхождений</t>
         </is>
       </c>
-      <c r="C90" s="30" t="n">
+      <c r="C90" s="33" t="n">
         <v>0.1</v>
       </c>
-      <c r="D90" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" s="30">
+      <c r="D90" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="33">
         <f>C90*D90</f>
         <v/>
       </c>
-      <c r="F90" s="25" t="n"/>
+      <c r="F90" s="28" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="31" t="n"/>
-      <c r="B91" s="32" t="inlineStr">
+      <c r="A91" s="34" t="n"/>
+      <c r="B91" s="35" t="inlineStr">
         <is>
           <t>Итоговое выполнение показателей</t>
         </is>
       </c>
-      <c r="C91" s="33">
+      <c r="C91" s="36">
         <f>SUM(C87:C90)</f>
         <v/>
       </c>
-      <c r="D91" s="31" t="n"/>
-      <c r="E91" s="34">
+      <c r="D91" s="34" t="n"/>
+      <c r="E91" s="37">
         <f>SUM(E87:E90)</f>
         <v/>
       </c>
-      <c r="F91" s="31" t="n"/>
+      <c r="F91" s="34" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="23" t="n"/>
-      <c r="B93" s="23" t="inlineStr">
+      <c r="A93" s="26" t="n"/>
+      <c r="B93" s="26" t="inlineStr">
         <is>
           <t>Аманбекова Айгуль — Руководитель отдела персонала · Персонал  [ПОДДЕРЖКА]</t>
         </is>
       </c>
-      <c r="C93" s="23" t="n"/>
-      <c r="D93" s="23" t="n"/>
-      <c r="E93" s="23" t="n"/>
-      <c r="F93" s="23" t="n"/>
+      <c r="C93" s="26" t="n"/>
+      <c r="D93" s="26" t="n"/>
+      <c r="E93" s="26" t="n"/>
+      <c r="F93" s="26" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="24" t="n"/>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="A94" s="27" t="n"/>
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>Вес</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>Выполнение, %</t>
         </is>
       </c>
-      <c r="E94" s="3" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t>Вклад</t>
         </is>
       </c>
-      <c r="F94" s="24" t="n"/>
+      <c r="F94" s="27" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="25" t="n"/>
-      <c r="B95" s="26" t="inlineStr">
+      <c r="A95" s="28" t="n"/>
+      <c r="B95" s="29" t="inlineStr">
         <is>
           <t>Чистая прибыль компании (общий)</t>
         </is>
       </c>
-      <c r="C95" s="27" t="n">
+      <c r="C95" s="30" t="n">
         <v>0.25</v>
       </c>
-      <c r="D95" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" s="27">
+      <c r="D95" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="30">
         <f>C95*D95</f>
         <v/>
       </c>
-      <c r="F95" s="25" t="n"/>
+      <c r="F95" s="28" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="25" t="n"/>
-      <c r="B96" s="29" t="inlineStr">
+      <c r="A96" s="28" t="n"/>
+      <c r="B96" s="32" t="inlineStr">
         <is>
           <t>Удержание персонала / текучесть</t>
         </is>
       </c>
-      <c r="C96" s="30" t="n">
+      <c r="C96" s="33" t="n">
         <v>0.25</v>
       </c>
-      <c r="D96" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" s="30">
+      <c r="D96" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="33">
         <f>C96*D96</f>
         <v/>
       </c>
-      <c r="F96" s="25" t="n"/>
+      <c r="F96" s="28" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="25" t="n"/>
-      <c r="B97" s="29" t="inlineStr">
+      <c r="A97" s="28" t="n"/>
+      <c r="B97" s="32" t="inlineStr">
         <is>
           <t>Срок закрытия ключевых вакансий</t>
         </is>
       </c>
-      <c r="C97" s="30" t="n">
+      <c r="C97" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="D97" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="30">
+      <c r="D97" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="33">
         <f>C97*D97</f>
         <v/>
       </c>
-      <c r="F97" s="25" t="n"/>
+      <c r="F97" s="28" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="25" t="n"/>
-      <c r="B98" s="29" t="inlineStr">
+      <c r="A98" s="28" t="n"/>
+      <c r="B98" s="32" t="inlineStr">
         <is>
           <t>Вовлечённость персонала (опрос)</t>
         </is>
       </c>
-      <c r="C98" s="30" t="n">
+      <c r="C98" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D98" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="30">
+      <c r="D98" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="33">
         <f>C98*D98</f>
         <v/>
       </c>
-      <c r="F98" s="25" t="n"/>
+      <c r="F98" s="28" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="25" t="n"/>
-      <c r="B99" s="29" t="inlineStr">
+      <c r="A99" s="28" t="n"/>
+      <c r="B99" s="32" t="inlineStr">
         <is>
           <t>Внедрение мотивации / бюджет фонда</t>
         </is>
       </c>
-      <c r="C99" s="30" t="n">
+      <c r="C99" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D99" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" s="30">
+      <c r="D99" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="33">
         <f>C99*D99</f>
         <v/>
       </c>
-      <c r="F99" s="25" t="n"/>
+      <c r="F99" s="28" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="31" t="n"/>
-      <c r="B100" s="32" t="inlineStr">
+      <c r="A100" s="34" t="n"/>
+      <c r="B100" s="35" t="inlineStr">
         <is>
           <t>Итоговое выполнение показателей</t>
         </is>
       </c>
-      <c r="C100" s="33">
+      <c r="C100" s="36">
         <f>SUM(C95:C99)</f>
         <v/>
       </c>
-      <c r="D100" s="31" t="n"/>
-      <c r="E100" s="34">
+      <c r="D100" s="34" t="n"/>
+      <c r="E100" s="37">
         <f>SUM(E95:E99)</f>
         <v/>
       </c>
-      <c r="F100" s="31" t="n"/>
+      <c r="F100" s="34" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="23" t="n"/>
-      <c r="B102" s="23" t="inlineStr">
+      <c r="A102" s="26" t="n"/>
+      <c r="B102" s="26" t="inlineStr">
         <is>
           <t>Байльденова Шолпан — Менеджер по персоналу · Персонал  [ПОДДЕРЖКА]</t>
         </is>
       </c>
-      <c r="C102" s="23" t="n"/>
-      <c r="D102" s="23" t="n"/>
-      <c r="E102" s="23" t="n"/>
-      <c r="F102" s="23" t="n"/>
+      <c r="C102" s="26" t="n"/>
+      <c r="D102" s="26" t="n"/>
+      <c r="E102" s="26" t="n"/>
+      <c r="F102" s="26" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="24" t="n"/>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="A103" s="27" t="n"/>
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C103" s="7" t="inlineStr">
         <is>
           <t>Вес</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="D103" s="7" t="inlineStr">
         <is>
           <t>Выполнение, %</t>
         </is>
       </c>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="E103" s="7" t="inlineStr">
         <is>
           <t>Вклад</t>
         </is>
       </c>
-      <c r="F103" s="24" t="n"/>
+      <c r="F103" s="27" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="25" t="n"/>
-      <c r="B104" s="26" t="inlineStr">
+      <c r="A104" s="28" t="n"/>
+      <c r="B104" s="29" t="inlineStr">
         <is>
           <t>Чистая прибыль компании (общий)</t>
         </is>
       </c>
-      <c r="C104" s="27" t="n">
+      <c r="C104" s="30" t="n">
         <v>0.25</v>
       </c>
-      <c r="D104" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="27">
+      <c r="D104" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="30">
         <f>C104*D104</f>
         <v/>
       </c>
-      <c r="F104" s="25" t="n"/>
+      <c r="F104" s="28" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="25" t="n"/>
-      <c r="B105" s="29" t="inlineStr">
+      <c r="A105" s="28" t="n"/>
+      <c r="B105" s="32" t="inlineStr">
         <is>
           <t>Срок закрытия вакансий</t>
         </is>
       </c>
-      <c r="C105" s="30" t="n">
+      <c r="C105" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="D105" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" s="30">
+      <c r="D105" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="33">
         <f>C105*D105</f>
         <v/>
       </c>
-      <c r="F105" s="25" t="n"/>
+      <c r="F105" s="28" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="25" t="n"/>
-      <c r="B106" s="29" t="inlineStr">
+      <c r="A106" s="28" t="n"/>
+      <c r="B106" s="32" t="inlineStr">
         <is>
           <t>Кадровый учёт без нарушений</t>
         </is>
       </c>
-      <c r="C106" s="30" t="n">
+      <c r="C106" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="D106" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" s="30">
+      <c r="D106" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="33">
         <f>C106*D106</f>
         <v/>
       </c>
-      <c r="F106" s="25" t="n"/>
+      <c r="F106" s="28" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="25" t="n"/>
-      <c r="B107" s="29" t="inlineStr">
+      <c r="A107" s="28" t="n"/>
+      <c r="B107" s="32" t="inlineStr">
         <is>
           <t>Точность расчёта зарплаты</t>
         </is>
       </c>
-      <c r="C107" s="30" t="n">
+      <c r="C107" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="D107" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" s="30">
+      <c r="D107" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="33">
         <f>C107*D107</f>
         <v/>
       </c>
-      <c r="F107" s="25" t="n"/>
+      <c r="F107" s="28" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="25" t="n"/>
-      <c r="B108" s="29" t="inlineStr">
+      <c r="A108" s="28" t="n"/>
+      <c r="B108" s="32" t="inlineStr">
         <is>
           <t>Адаптация новых сотрудников</t>
         </is>
       </c>
-      <c r="C108" s="30" t="n">
+      <c r="C108" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D108" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="30">
+      <c r="D108" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="33">
         <f>C108*D108</f>
         <v/>
       </c>
-      <c r="F108" s="25" t="n"/>
+      <c r="F108" s="28" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="31" t="n"/>
-      <c r="B109" s="32" t="inlineStr">
+      <c r="A109" s="34" t="n"/>
+      <c r="B109" s="35" t="inlineStr">
         <is>
           <t>Итоговое выполнение показателей</t>
         </is>
       </c>
-      <c r="C109" s="33">
+      <c r="C109" s="36">
         <f>SUM(C104:C108)</f>
         <v/>
       </c>
-      <c r="D109" s="31" t="n"/>
-      <c r="E109" s="34">
+      <c r="D109" s="34" t="n"/>
+      <c r="E109" s="37">
         <f>SUM(E104:E108)</f>
         <v/>
       </c>
-      <c r="F109" s="31" t="n"/>
+      <c r="F109" s="34" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="23" t="n"/>
-      <c r="B111" s="23" t="inlineStr">
+      <c r="A111" s="26" t="n"/>
+      <c r="B111" s="26" t="inlineStr">
         <is>
           <t>Ташметов Сакен — Юрист · Юридический  [ПОДДЕРЖКА]</t>
         </is>
       </c>
-      <c r="C111" s="23" t="n"/>
-      <c r="D111" s="23" t="n"/>
-      <c r="E111" s="23" t="n"/>
-      <c r="F111" s="23" t="n"/>
+      <c r="C111" s="26" t="n"/>
+      <c r="D111" s="26" t="n"/>
+      <c r="E111" s="26" t="n"/>
+      <c r="F111" s="26" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="24" t="n"/>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="A112" s="27" t="n"/>
+      <c r="B112" s="7" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="C112" s="7" t="inlineStr">
         <is>
           <t>Вес</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
+      <c r="D112" s="7" t="inlineStr">
         <is>
           <t>Выполнение, %</t>
         </is>
       </c>
-      <c r="E112" s="3" t="inlineStr">
+      <c r="E112" s="7" t="inlineStr">
         <is>
           <t>Вклад</t>
         </is>
       </c>
-      <c r="F112" s="24" t="n"/>
+      <c r="F112" s="27" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="25" t="n"/>
-      <c r="B113" s="26" t="inlineStr">
+      <c r="A113" s="28" t="n"/>
+      <c r="B113" s="29" t="inlineStr">
         <is>
           <t>Чистая прибыль компании (общий)</t>
         </is>
       </c>
-      <c r="C113" s="27" t="n">
+      <c r="C113" s="30" t="n">
         <v>0.25</v>
       </c>
-      <c r="D113" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E113" s="27">
+      <c r="D113" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="30">
         <f>C113*D113</f>
         <v/>
       </c>
-      <c r="F113" s="25" t="n"/>
+      <c r="F113" s="28" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="25" t="n"/>
-      <c r="B114" s="29" t="inlineStr">
+      <c r="A114" s="28" t="n"/>
+      <c r="B114" s="32" t="inlineStr">
         <is>
           <t>Взысканная дебиторка / споры</t>
         </is>
       </c>
-      <c r="C114" s="30" t="n">
+      <c r="C114" s="33" t="n">
         <v>0.25</v>
       </c>
-      <c r="D114" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" s="30">
+      <c r="D114" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="33">
         <f>C114*D114</f>
         <v/>
       </c>
-      <c r="F114" s="25" t="n"/>
+      <c r="F114" s="28" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="25" t="n"/>
-      <c r="B115" s="29" t="inlineStr">
+      <c r="A115" s="28" t="n"/>
+      <c r="B115" s="32" t="inlineStr">
         <is>
           <t>Согласование договоров в срок</t>
         </is>
       </c>
-      <c r="C115" s="30" t="n">
+      <c r="C115" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="D115" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" s="30">
+      <c r="D115" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="33">
         <f>C115*D115</f>
         <v/>
       </c>
-      <c r="F115" s="25" t="n"/>
+      <c r="F115" s="28" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="25" t="n"/>
-      <c r="B116" s="29" t="inlineStr">
+      <c r="A116" s="28" t="n"/>
+      <c r="B116" s="32" t="inlineStr">
         <is>
           <t>Юридические риски: штрафы</t>
         </is>
       </c>
-      <c r="C116" s="30" t="n">
+      <c r="C116" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D116" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" s="30">
+      <c r="D116" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="33">
         <f>C116*D116</f>
         <v/>
       </c>
-      <c r="F116" s="25" t="n"/>
+      <c r="F116" s="28" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="25" t="n"/>
-      <c r="B117" s="29" t="inlineStr">
+      <c r="A117" s="28" t="n"/>
+      <c r="B117" s="32" t="inlineStr">
         <is>
           <t>Сопровождение сделок и перевозок</t>
         </is>
       </c>
-      <c r="C117" s="30" t="n">
+      <c r="C117" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D117" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E117" s="30">
+      <c r="D117" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="33">
         <f>C117*D117</f>
         <v/>
       </c>
-      <c r="F117" s="25" t="n"/>
+      <c r="F117" s="28" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="31" t="n"/>
-      <c r="B118" s="32" t="inlineStr">
+      <c r="A118" s="34" t="n"/>
+      <c r="B118" s="35" t="inlineStr">
         <is>
           <t>Итоговое выполнение показателей</t>
         </is>
       </c>
-      <c r="C118" s="33">
+      <c r="C118" s="36">
         <f>SUM(C113:C117)</f>
         <v/>
       </c>
-      <c r="D118" s="31" t="n"/>
-      <c r="E118" s="34">
+      <c r="D118" s="34" t="n"/>
+      <c r="E118" s="37">
         <f>SUM(E113:E117)</f>
         <v/>
       </c>
-      <c r="F118" s="31" t="n"/>
+      <c r="F118" s="34" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3497,7 +3656,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>Справочник показателей эффективности (транспортно-логистическая компания)</t>
         </is>
@@ -3511,800 +3670,800 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Функция / роль</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Рекоменд. вес, %</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Источник факта</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Тип</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Руководство</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Чистая прибыль компании к плану</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>% к плану</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>40–50</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Управл. отчётность</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>команд.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Руководство</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Выручка к плану</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>% к плану</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>15–20</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Отчёт о продажах</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>команд.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Руководство</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Развитие: новые направления/клиенты</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>% этапов</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>15–20</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>План развития</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>индив.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Финансы</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Запас денежных средств / кассовые разрывы</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>мес.</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>Движение средств</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>команд.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Финансы</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Период оборота дебиторской задолженности</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>дни</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>15–20</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Реестр расчётов</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>команд.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Финансы</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Точность бюджета (отклонение факт/план)</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>План/факт</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>индив.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Операции</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Валовая прибыль по операциям</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>млн ₸</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>Себестоимость</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>команд.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Операции</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Соблюдение сроков (в срок и в полном объёме)</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>% рейсов</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>Учёт перевозок</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>команд.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Операции</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Себестоимость на тонну/километр</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>₸</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Себестоимость</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>индив.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Операции</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Безопасность: происшествия / охрана труда</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>кол-во</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>Служба безопасности</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>команд.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Валовая маржа по своим перевозкам</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>₸ / % ≥K×стоим.</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Себестоимость</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>индив.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>Объём организованных перевозок к норме</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>рейсы / тонны</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>Учёт перевозок</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>индив.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Соблюдение сроков доставки</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>% в срок</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Учёт перевозок</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>индив.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Загрузка транспорта / порожний пробег</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>10–15</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>Учёт перевозок</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>индив.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Логистика</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Сохранность груза и уровень претензий</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>% / кол-во</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Отдел рекламаций</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>индив.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Расчёты/закрытие</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Валовая прибыль по закрытым перевозкам</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>₸</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>Учёт/отчётность</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>индив.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Расчёты/закрытие</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Собираемость оплаты в срок</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>% в срок</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Реестр расчётов</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>индив.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Расчёты/закрытие</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>Срок закрытия документов</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>дни</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>Документооборот</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>индив.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Персонал</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Удержание ключевого персонала / текучесть</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Кадровый учёт</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>команд.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Персонал</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>Срок закрытия вакансий</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>дни</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>Отчёт по подбору</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>индив.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Персонал</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Точность и своевременность расчёта зарплаты</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>Бухгалтерия</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>индив.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Юридический</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>Взысканная дебиторская задолженность / споры</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>₸ / %</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>Претензии</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>индив.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Юридический</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Согласование договоров в срок</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>дни / %</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>Реестр договоров</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>индив.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Все роли</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>Чистая прибыль компании (общий показатель)</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>% к плану</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>Управл. отчётность</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>команд.</t>
         </is>
